--- a/Kaggle_12Week_Checklist.xlsx
+++ b/Kaggle_12Week_Checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ZeroPrograming\JupyterNotebook\Retail Store Inventory and Demand Forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39409BC-F1A5-4977-BDD4-71C9DFBEA382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2B9ADE-11AC-4F84-9099-CFC27539027D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="187">
   <si>
     <t>Week</t>
   </si>
@@ -561,9 +561,6 @@
   </si>
   <si>
     <t>⑥ 撰写分析总结：类别特征对销量的影响</t>
-  </si>
-  <si>
-    <t>⑤ 绘制类别销量变化趋势</t>
   </si>
   <si>
     <t>③ 检查类别间差异是否显著（ANOVA）</t>
@@ -579,6 +576,18 @@
   </si>
   <si>
     <t>④ 计算类别占比与贡献度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>⑤ 绘制类别销量变化趋势</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>✔</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +596,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="[$-409]yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -753,23 +762,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -779,7 +788,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -792,6 +801,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -801,25 +829,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1210,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>184</v>
       </c>
       <c r="E5" s="7">
         <v>45944</v>
@@ -1226,7 +1238,9 @@
       <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="6" t="s">
+        <v>184</v>
+      </c>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1905,19 +1919,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1928,11 +1942,11 @@
       <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>124</v>
+      <c r="D2" s="28" t="s">
+        <v>186</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>124</v>
@@ -1942,7 +1956,7 @@
       <c r="A3" s="23"/>
       <c r="B3" s="23"/>
       <c r="C3" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>124</v>
@@ -1955,7 +1969,7 @@
       <c r="A4" s="23"/>
       <c r="B4" s="23"/>
       <c r="C4" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>124</v>
@@ -1968,7 +1982,7 @@
       <c r="A5" s="23"/>
       <c r="B5" s="23"/>
       <c r="C5" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>124</v>
@@ -1980,8 +1994,8 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
       <c r="B6" s="23"/>
-      <c r="C6" s="27" t="s">
-        <v>184</v>
+      <c r="C6" s="21" t="s">
+        <v>183</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>124</v>
@@ -1993,8 +2007,8 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="16" t="s">
-        <v>180</v>
+      <c r="C7" s="21" t="s">
+        <v>185</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>124</v>
@@ -2017,13 +2031,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="25">
         <v>1</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="20" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="17" t="s">
@@ -2034,8 +2048,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="17" t="s">
         <v>178</v>
       </c>
@@ -2047,8 +2061,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="17" t="s">
         <v>177</v>
       </c>
@@ -2060,8 +2074,8 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="17" t="s">
         <v>176</v>
       </c>
@@ -2073,8 +2087,8 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="17" t="s">
         <v>175</v>
       </c>
@@ -2086,8 +2100,8 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="17" t="s">
         <v>174</v>
       </c>
@@ -2099,8 +2113,8 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
       <c r="C15" s="17" t="s">
         <v>173</v>
       </c>
